--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0001T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0001T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.60466385987378</v>
+        <v>2.048257877229489</v>
       </c>
       <c r="D2" t="n">
-        <v>6.041522986797286</v>
+        <v>0.981747485354559</v>
       </c>
       <c r="E2" t="n">
-        <v>6.615345671624452</v>
+        <v>1.074993671638973</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7295117793787881</v>
+        <v>0.118545664149053</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1.541930938923066</v>
+        <v>0.2505637775749981</v>
       </c>
       <c r="D3" t="n">
-        <v>5.099019513592784</v>
+        <v>0.8285906709588275</v>
       </c>
       <c r="E3" t="n">
-        <v>6.615345671624452</v>
+        <v>1.074993671638973</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7295117793787881</v>
+        <v>0.118545664149053</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.446193297481017</v>
+        <v>1.535006410840665</v>
       </c>
       <c r="D4" t="n">
-        <v>6.868364112580993</v>
+        <v>1.116109168294411</v>
       </c>
       <c r="E4" t="n">
-        <v>6.615345671624452</v>
+        <v>1.074993671638973</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7295117793787881</v>
+        <v>0.118545664149053</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4.215008804529109</v>
+        <v>0.6849389307359802</v>
       </c>
       <c r="D5" t="n">
-        <v>4.845989012924377</v>
+        <v>0.7874732146002112</v>
       </c>
       <c r="E5" t="n">
-        <v>6.615345671624452</v>
+        <v>1.074993671638973</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7295117793787881</v>
+        <v>0.118545664149053</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.36278508739191</v>
+        <v>3.308952576701186</v>
       </c>
       <c r="D6" t="n">
-        <v>6.048136829615664</v>
+        <v>0.9828222348125454</v>
       </c>
       <c r="E6" t="n">
-        <v>6.615345671624452</v>
+        <v>1.074993671638973</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7295117793787881</v>
+        <v>0.118545664149053</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
